--- a/data/trans_orig/P16A09-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A09-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13284</t>
+          <t>12517</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31008</t>
+          <t>29759</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17462</t>
+          <t>17322</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36151</t>
+          <t>36897</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,47 +783,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>46198</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>35148</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>59810</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>2,54%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>46198</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>35930</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>61383</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>661986</t>
+          <t>663235</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>679710</t>
+          <t>680477</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>652200</t>
+          <t>651454</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>670889</t>
+          <t>671029</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,47 +896,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>97,48%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1335147</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>1321535</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1346197</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>96,66%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>95,67%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>97,46%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1330</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1335147</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1319962</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1345415</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>96,66%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>95,56%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16721</t>
+          <t>16858</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37209</t>
+          <t>37649</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32311</t>
+          <t>33357</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59988</t>
+          <t>61109</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>55845</t>
+          <t>56945</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89801</t>
+          <t>91344</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>924591</t>
+          <t>924151</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>945079</t>
+          <t>944942</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>908405</t>
+          <t>907284</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>936082</t>
+          <t>935036</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1840392</t>
+          <t>1838849</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1874348</t>
+          <t>1873248</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10604</t>
+          <t>10220</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27636</t>
+          <t>27538</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30646</t>
+          <t>30256</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56008</t>
+          <t>55210</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46110</t>
+          <t>43358</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74876</t>
+          <t>74974</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>650873</t>
+          <t>650971</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667905</t>
+          <t>668289</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>627833</t>
+          <t>628631</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>653195</t>
+          <t>653585</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1287474</t>
+          <t>1287376</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1316240</t>
+          <t>1318992</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23458</t>
+          <t>21884</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44767</t>
+          <t>43951</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44911</t>
+          <t>43109</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>74936</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73171</t>
+          <t>74362</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>110930</t>
+          <t>110706</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>897455</t>
+          <t>898271</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>918764</t>
+          <t>920338</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>962186</t>
+          <t>963676</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>993701</t>
+          <t>995503</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1869904</t>
+          <t>1870128</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1907663</t>
+          <t>1906472</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77076</t>
+          <t>78300</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>115878</t>
+          <t>114764</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>147850</t>
+          <t>146473</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>199364</t>
+          <t>198455</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>235279</t>
+          <t>236178</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>298426</t>
+          <t>301417</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3159647</t>
+          <t>3160761</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3198449</t>
+          <t>3197225</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3179833</t>
+          <t>3180742</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3231347</t>
+          <t>3232724</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6356296</t>
+          <t>6353305</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6419443</t>
+          <t>6418544</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21181</t>
+          <t>22255</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25719</t>
+          <t>26453</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>50429</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37187</t>
+          <t>38011</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63648</t>
+          <t>64768</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>679583</t>
+          <t>678509</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>694383</t>
+          <t>693564</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>642405</t>
+          <t>641883</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>666593</t>
+          <t>665859</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1329427</t>
+          <t>1328307</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1355888</t>
+          <t>1355064</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16061</t>
+          <t>15369</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35859</t>
+          <t>35242</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51567</t>
+          <t>51156</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83276</t>
+          <t>82820</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72537</t>
+          <t>70514</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110119</t>
+          <t>109780</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>982088</t>
+          <t>982705</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1001886</t>
+          <t>1002578</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>944499</t>
+          <t>944955</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>976208</t>
+          <t>976619</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1935604</t>
+          <t>1935943</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1973186</t>
+          <t>1975209</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25365</t>
+          <t>25612</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25893</t>
+          <t>26280</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49580</t>
+          <t>49584</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37980</t>
+          <t>36856</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68941</t>
+          <t>67541</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>731173</t>
+          <t>730926</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>749272</t>
+          <t>749223</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>726703</t>
+          <t>726699</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>750390</t>
+          <t>750003</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1463880</t>
+          <t>1465280</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1494841</t>
+          <t>1495965</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11753</t>
+          <t>11777</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32035</t>
+          <t>32172</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50314</t>
+          <t>52030</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83341</t>
+          <t>85645</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69715</t>
+          <t>70500</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>108033</t>
+          <t>109531</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>911904</t>
+          <t>911767</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>932186</t>
+          <t>932162</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>965422</t>
+          <t>963118</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>998449</t>
+          <t>996733</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1884670</t>
+          <t>1883172</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1922988</t>
+          <t>1922203</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55242</t>
+          <t>54702</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>91401</t>
+          <t>90999</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>181182</t>
+          <t>177098</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>235216</t>
+          <t>236451</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>245081</t>
+          <t>246216</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>315223</t>
+          <t>313136</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3327787</t>
+          <t>3328189</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3363946</t>
+          <t>3364486</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3309918</t>
+          <t>3308683</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3363952</t>
+          <t>3368036</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6649099</t>
+          <t>6651186</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6719241</t>
+          <t>6718106</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15901</t>
+          <t>15481</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17724</t>
+          <t>17287</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39296</t>
+          <t>38182</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,47 +4677,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,67%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>35465</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>24971</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>49259</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>2,63%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>35465</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>24093</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>48707</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>658899</t>
+          <t>659319</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>670821</t>
+          <t>670695</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>633543</t>
+          <t>634657</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>655115</t>
+          <t>655552</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,47 +4790,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>97,43%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1312174</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>1298380</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1322668</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>97,37%</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1285</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1312174</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1298932</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1323546</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>97,37%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26082</t>
+          <t>24751</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28097</t>
+          <t>29090</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54233</t>
+          <t>56728</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41184</t>
+          <t>42068</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71814</t>
+          <t>71571</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>996349</t>
+          <t>997680</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1013189</t>
+          <t>1013720</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>988680</t>
+          <t>986185</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1014816</t>
+          <t>1013823</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1993530</t>
+          <t>1993773</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2024160</t>
+          <t>2023276</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7925</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23325</t>
+          <t>21756</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19475</t>
+          <t>20430</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42050</t>
+          <t>42296</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30996</t>
+          <t>30689</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57078</t>
+          <t>58595</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>736227</t>
+          <t>737796</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>751627</t>
+          <t>751877</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>742961</t>
+          <t>742715</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>765536</t>
+          <t>764581</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1487485</t>
+          <t>1485968</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1513567</t>
+          <t>1513874</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15882</t>
+          <t>15665</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26273</t>
+          <t>26129</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51448</t>
+          <t>52653</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32650</t>
+          <t>31907</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60888</t>
+          <t>61288</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>921685</t>
+          <t>921902</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>934097</t>
+          <t>933759</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>992331</t>
+          <t>991126</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1017506</t>
+          <t>1017650</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1920458</t>
+          <t>1920058</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1948696</t>
+          <t>1949439</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34225</t>
+          <t>33114</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60827</t>
+          <t>59638</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>110223</t>
+          <t>111719</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>158235</t>
+          <t>159042</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>154896</t>
+          <t>152690</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>209063</t>
+          <t>209726</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3333523</t>
+          <t>3334712</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3360125</t>
+          <t>3361236</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3386307</t>
+          <t>3385500</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3434319</t>
+          <t>3432823</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6729829</t>
+          <t>6729166</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6783996</t>
+          <t>6786202</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>9549</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24652</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33759</t>
+          <t>34444</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55069</t>
+          <t>52640</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45894</t>
+          <t>45947</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70918</t>
+          <t>71062</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>610299</t>
+          <t>610272</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>625671</t>
+          <t>625402</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>620353</t>
+          <t>622782</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>641663</t>
+          <t>640978</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1239455</t>
+          <t>1239311</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1264479</t>
+          <t>1264426</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,49%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26504</t>
+          <t>26079</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36653</t>
+          <t>36395</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56130</t>
+          <t>56422</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41547</t>
+          <t>41750</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77499</t>
+          <t>77065</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1166360</t>
+          <t>1166785</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1185247</t>
+          <t>1186573</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>901976</t>
+          <t>901684</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>921453</t>
+          <t>921711</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2073472</t>
+          <t>2073906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2109424</t>
+          <t>2109221</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>7057</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20052</t>
+          <t>20114</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13484</t>
+          <t>13370</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41157</t>
+          <t>42205</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25128</t>
+          <t>26371</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53798</t>
+          <t>54154</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>683632</t>
+          <t>683570</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>697148</t>
+          <t>696627</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>890768</t>
+          <t>889720</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>918441</t>
+          <t>918555</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1581810</t>
+          <t>1581454</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1610480</t>
+          <t>1609237</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10290</t>
+          <t>10984</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24966</t>
+          <t>25770</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53768</t>
+          <t>52725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89959</t>
+          <t>88221</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71695</t>
+          <t>71120</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109028</t>
+          <t>108913</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>901149</t>
+          <t>900345</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>915825</t>
+          <t>915131</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1001415</t>
+          <t>1003153</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1037606</t>
+          <t>1038649</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1908461</t>
+          <t>1908576</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1945794</t>
+          <t>1946369</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45805</t>
+          <t>45136</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79269</t>
+          <t>78273</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>152825</t>
+          <t>153628</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>215091</t>
+          <t>214832</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>211225</t>
+          <t>212623</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>278841</t>
+          <t>282968</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3378346</t>
+          <t>3379342</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3411810</t>
+          <t>3412479</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3441736</t>
+          <t>3441995</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3504002</t>
+          <t>3503199</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6835600</t>
+          <t>6831473</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6903216</t>
+          <t>6901818</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A09-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A09-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12517</t>
+          <t>12657</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29759</t>
+          <t>30490</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17322</t>
+          <t>17814</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36897</t>
+          <t>37169</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35148</t>
+          <t>34191</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59810</t>
+          <t>60678</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>663235</t>
+          <t>662504</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>680477</t>
+          <t>680337</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>651454</t>
+          <t>651182</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>671029</t>
+          <t>670537</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1321535</t>
+          <t>1320667</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1346197</t>
+          <t>1347154</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16858</t>
+          <t>16845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37649</t>
+          <t>37218</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33357</t>
+          <t>31783</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61109</t>
+          <t>59566</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56945</t>
+          <t>55438</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91344</t>
+          <t>87852</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>924151</t>
+          <t>924582</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>944942</t>
+          <t>944955</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>907284</t>
+          <t>908827</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>935036</t>
+          <t>936610</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1838849</t>
+          <t>1842341</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1873248</t>
+          <t>1874755</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10220</t>
+          <t>10279</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27538</t>
+          <t>27596</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30256</t>
+          <t>30186</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55210</t>
+          <t>54839</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43358</t>
+          <t>45408</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74974</t>
+          <t>73202</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>650971</t>
+          <t>650913</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>668289</t>
+          <t>668230</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>628631</t>
+          <t>629002</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>653585</t>
+          <t>653655</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1287376</t>
+          <t>1289148</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1318992</t>
+          <t>1316942</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21884</t>
+          <t>22197</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43951</t>
+          <t>43205</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43109</t>
+          <t>44896</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74936</t>
+          <t>76299</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74362</t>
+          <t>72964</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>110706</t>
+          <t>111552</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>898271</t>
+          <t>899017</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>920338</t>
+          <t>920025</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>963676</t>
+          <t>962313</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>995503</t>
+          <t>993716</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1870128</t>
+          <t>1869282</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1906472</t>
+          <t>1907870</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78300</t>
+          <t>78523</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>114764</t>
+          <t>115374</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>146473</t>
+          <t>147081</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>198455</t>
+          <t>200905</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>236178</t>
+          <t>235431</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>301417</t>
+          <t>299774</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3160761</t>
+          <t>3160151</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3197225</t>
+          <t>3197002</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3180742</t>
+          <t>3178292</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3232724</t>
+          <t>3232116</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6353305</t>
+          <t>6354948</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6418544</t>
+          <t>6419291</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22255</t>
+          <t>21525</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26453</t>
+          <t>26417</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50429</t>
+          <t>52186</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38011</t>
+          <t>36745</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64768</t>
+          <t>65158</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>678509</t>
+          <t>679239</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>693564</t>
+          <t>694209</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>641883</t>
+          <t>640126</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>665859</t>
+          <t>665895</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1328307</t>
+          <t>1327917</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1355064</t>
+          <t>1356330</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15369</t>
+          <t>16030</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35242</t>
+          <t>35394</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51156</t>
+          <t>51612</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82820</t>
+          <t>83490</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70514</t>
+          <t>71006</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109780</t>
+          <t>108744</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>982705</t>
+          <t>982553</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1002578</t>
+          <t>1001917</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>944955</t>
+          <t>944285</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>976619</t>
+          <t>976163</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1935943</t>
+          <t>1936979</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1975209</t>
+          <t>1974717</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>7603</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25612</t>
+          <t>25387</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26280</t>
+          <t>25815</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49584</t>
+          <t>49545</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36856</t>
+          <t>37962</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67541</t>
+          <t>68312</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>730926</t>
+          <t>731151</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>749223</t>
+          <t>748935</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>726699</t>
+          <t>726738</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>750003</t>
+          <t>750468</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1465280</t>
+          <t>1464509</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1495965</t>
+          <t>1494859</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11777</t>
+          <t>13251</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32172</t>
+          <t>33586</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52030</t>
+          <t>52490</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85645</t>
+          <t>84432</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70500</t>
+          <t>69425</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109531</t>
+          <t>110420</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>911767</t>
+          <t>910353</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>932162</t>
+          <t>930688</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>963118</t>
+          <t>964331</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>996733</t>
+          <t>996273</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1883172</t>
+          <t>1882283</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1922203</t>
+          <t>1923278</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54702</t>
+          <t>56285</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>90999</t>
+          <t>91026</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>177098</t>
+          <t>178549</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>236451</t>
+          <t>236700</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>246216</t>
+          <t>247370</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>313136</t>
+          <t>309906</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3328189</t>
+          <t>3328162</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3364486</t>
+          <t>3362903</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3308683</t>
+          <t>3308434</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3368036</t>
+          <t>3366585</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6651186</t>
+          <t>6654416</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6718106</t>
+          <t>6716952</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15481</t>
+          <t>15982</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17287</t>
+          <t>17090</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>39658</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24971</t>
+          <t>25470</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49259</t>
+          <t>48558</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>659319</t>
+          <t>658818</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>670695</t>
+          <t>670588</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>634657</t>
+          <t>633181</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>655552</t>
+          <t>655749</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1298380</t>
+          <t>1299081</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1322668</t>
+          <t>1322169</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>9223</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24751</t>
+          <t>26451</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29090</t>
+          <t>28868</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56728</t>
+          <t>55901</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42068</t>
+          <t>42729</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71571</t>
+          <t>72127</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>997680</t>
+          <t>995980</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1013720</t>
+          <t>1013208</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>986185</t>
+          <t>987012</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1013823</t>
+          <t>1014045</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1993773</t>
+          <t>1993217</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2023276</t>
+          <t>2022615</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7675</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21756</t>
+          <t>21376</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20430</t>
+          <t>20460</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42296</t>
+          <t>43172</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30689</t>
+          <t>31174</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58595</t>
+          <t>58530</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>737796</t>
+          <t>738176</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>751877</t>
+          <t>752337</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>742715</t>
+          <t>741839</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>764581</t>
+          <t>764551</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1485968</t>
+          <t>1486033</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1513874</t>
+          <t>1513389</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15665</t>
+          <t>16116</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26129</t>
+          <t>25978</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52653</t>
+          <t>52451</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31907</t>
+          <t>33354</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61288</t>
+          <t>61563</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>921902</t>
+          <t>921451</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>933759</t>
+          <t>933744</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>991126</t>
+          <t>991328</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1017650</t>
+          <t>1017801</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1920058</t>
+          <t>1919783</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1949439</t>
+          <t>1947992</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33114</t>
+          <t>33086</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59638</t>
+          <t>60175</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>111719</t>
+          <t>110235</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>159042</t>
+          <t>158867</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>152690</t>
+          <t>154872</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>209726</t>
+          <t>206987</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3334712</t>
+          <t>3334175</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3361236</t>
+          <t>3361264</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3385500</t>
+          <t>3385675</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3432823</t>
+          <t>3434307</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6729166</t>
+          <t>6731905</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6786202</t>
+          <t>6784020</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -6569,17 +6569,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15391</t>
+          <t>16698</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>10255</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>26521</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42454</t>
+          <t>47321</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34444</t>
+          <t>37974</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52640</t>
+          <t>59762</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>57845</t>
+          <t>64019</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45947</t>
+          <t>51220</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71062</t>
+          <t>79023</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -6682,17 +6682,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>619560</t>
+          <t>673517</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>610272</t>
+          <t>663694</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>625402</t>
+          <t>679960</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>632968</t>
+          <t>685461</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>622782</t>
+          <t>673020</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>640978</t>
+          <t>694808</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1252528</t>
+          <t>1358978</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1239311</t>
+          <t>1343974</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1264426</t>
+          <t>1371777</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634951</t>
+          <t>690215</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634951</t>
+          <t>690215</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634951</t>
+          <t>690215</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310373</t>
+          <t>1422997</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310373</t>
+          <t>1422997</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310373</t>
+          <t>1422997</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>17936</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>11571</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26079</t>
+          <t>28688</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>45438</t>
+          <t>51402</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36395</t>
+          <t>41188</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56422</t>
+          <t>62896</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>62055</t>
+          <t>69338</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41750</t>
+          <t>56800</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77065</t>
+          <t>84632</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1176247</t>
+          <t>1030981</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1166785</t>
+          <t>1020229</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1186573</t>
+          <t>1037346</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>912668</t>
+          <t>1019436</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>901684</t>
+          <t>1007942</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>921711</t>
+          <t>1029650</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2088916</t>
+          <t>2050417</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2073906</t>
+          <t>2035123</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2109221</t>
+          <t>2062955</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11619</t>
+          <t>12569</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7057</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20114</t>
+          <t>21546</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28759</t>
+          <t>32851</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13370</t>
+          <t>24150</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42205</t>
+          <t>42144</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>40378</t>
+          <t>45420</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26371</t>
+          <t>34874</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54154</t>
+          <t>57166</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>692065</t>
+          <t>789517</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>683570</t>
+          <t>780540</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>696627</t>
+          <t>794885</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>903166</t>
+          <t>777939</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>889720</t>
+          <t>768646</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>918555</t>
+          <t>786640</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1595230</t>
+          <t>1567455</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1581454</t>
+          <t>1555709</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1609237</t>
+          <t>1578001</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>931925</t>
+          <t>810790</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>931925</t>
+          <t>810790</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>931925</t>
+          <t>810790</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1635608</t>
+          <t>1612875</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1635608</t>
+          <t>1612875</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1635608</t>
+          <t>1612875</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16982</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10984</t>
+          <t>12373</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25770</t>
+          <t>28029</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>69682</t>
+          <t>72161</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52725</t>
+          <t>60071</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88221</t>
+          <t>87350</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>86664</t>
+          <t>90758</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71120</t>
+          <t>76035</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>108913</t>
+          <t>108439</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>909133</t>
+          <t>970655</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>900345</t>
+          <t>961223</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>915131</t>
+          <t>976879</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1021692</t>
+          <t>1044870</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1003153</t>
+          <t>1029681</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1038649</t>
+          <t>1056960</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1930825</t>
+          <t>2015525</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1908576</t>
+          <t>1997844</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1946369</t>
+          <t>2030248</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926115</t>
+          <t>989252</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926115</t>
+          <t>989252</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926115</t>
+          <t>989252</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2017489</t>
+          <t>2106283</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2017489</t>
+          <t>2106283</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2017489</t>
+          <t>2106283</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>60609</t>
+          <t>65800</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45136</t>
+          <t>52578</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78273</t>
+          <t>83495</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>186333</t>
+          <t>203735</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>153628</t>
+          <t>182405</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>214832</t>
+          <t>226977</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>246942</t>
+          <t>269535</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>212623</t>
+          <t>242954</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>282968</t>
+          <t>296333</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3397006</t>
+          <t>3464669</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3379342</t>
+          <t>3446974</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3412479</t>
+          <t>3477891</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3470494</t>
+          <t>3527706</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3441995</t>
+          <t>3504464</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3503199</t>
+          <t>3549036</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6867499</t>
+          <t>6992375</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6831473</t>
+          <t>6965577</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6901818</t>
+          <t>7018956</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3457615</t>
+          <t>3530469</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3457615</t>
+          <t>3530469</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3457615</t>
+          <t>3530469</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3656827</t>
+          <t>3731441</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3656827</t>
+          <t>3731441</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3656827</t>
+          <t>3731441</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7114441</t>
+          <t>7261910</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7114441</t>
+          <t>7261910</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7114441</t>
+          <t>7261910</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
